--- a/Ms-Excel/Excel+Report+2.xlsx
+++ b/Ms-Excel/Excel+Report+2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\topna\OneDrive\Desktop\All\Unedited Excel Videos\Excel Report 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics-KrishNaik Course\Ms-Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4290AD4F-2212-4EE0-819D-2213EDBF8B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6A845E-1E6B-40F6-B742-6EFA14E6BB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Production Dataset" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
